--- a/artfynd/A 20822-2024 artfynd.xlsx
+++ b/artfynd/A 20822-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>80631977</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485601.7372936817</v>
+        <v>485602</v>
       </c>
       <c r="R2" t="n">
-        <v>6438471.016074504</v>
+        <v>6438471</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>80631978</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485665.9379895267</v>
+        <v>485666</v>
       </c>
       <c r="R3" t="n">
-        <v>6438647.895292447</v>
+        <v>6438648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2019-09-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +870,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>80631980</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fålarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485568</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6438512</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-09-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-09-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>

--- a/artfynd/A 20822-2024 artfynd.xlsx
+++ b/artfynd/A 20822-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,6 +975,157 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135114107</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45050</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sörgården, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485583</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6438496</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Torr silikatgräsmark med tall</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>röllika</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Achillea millefolium</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Blomma på levande ört</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Flower on living herb/grass # Achillea millefolium</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Agnes Lindskog</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Agnes Lindskog</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20822-2024 artfynd.xlsx
+++ b/artfynd/A 20822-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80631977</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80631978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80631980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135114107</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 20822-2024 artfynd.xlsx
+++ b/artfynd/A 20822-2024 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>135114107</v>
       </c>
       <c r="B5" t="n">
-        <v>45050</v>
+        <v>45055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
